--- a/astro-site/public/dl/guia-restaurante-japones/calculadora-ticket-medio.xlsx
+++ b/astro-site/public/dl/guia-restaurante-japones/calculadora-ticket-medio.xlsx
@@ -499,9 +499,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -521,6 +521,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -549,10 +550,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-japones · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -561,7 +571,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -570,7 +589,7 @@
   <sheetPr>
     <tabColor rgb="0000BCD4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -593,6 +612,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -683,6 +704,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
@@ -696,7 +718,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -705,7 +736,7 @@
   <sheetPr>
     <tabColor rgb="00FFC107"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -728,6 +759,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -756,7 +789,7 @@
       </c>
       <c r="B7" s="11">
         <f>B5-B6</f>
-        <v/>
+        <v>9.0</v>
       </c>
     </row>
     <row r="8">
@@ -767,7 +800,7 @@
       </c>
       <c r="B8" s="12">
         <f>B7/B5</f>
-        <v/>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +831,7 @@
       </c>
       <c r="B11" s="11">
         <f>B9-B10</f>
-        <v/>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12">
@@ -839,7 +872,7 @@
       </c>
       <c r="B15" s="11">
         <f>(B5*B12+B9*B13)*B14</f>
-        <v/>
+        <v>18200.0</v>
       </c>
     </row>
   </sheetData>
@@ -847,6 +880,15 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>